--- a/Outputs/PtX_demand_DK.xlsx
+++ b/Outputs/PtX_demand_DK.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0004249492896250961</v>
-      </c>
+      <c r="C2" t="n">
+        <v>0.0006444730100779027</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.005579396866169524</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0007974757626754852</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1.306336170096178e-09</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0001748509948835993</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,17 +522,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0004249492896250961</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1.306336170096178e-09</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0001748509948835993</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,7 +557,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -570,7 +576,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -578,24 +584,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.0003844825721781027</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0001111623516295486</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>3.373774600869086e-05</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -603,14 +603,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.0003844825721781027</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.001635641213188201</v>
+        <v>0.0001111623516295486</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.0001334526910548289</v>
+        <v>3.373774600869086e-05</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -618,7 +620,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -627,17 +629,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.001635641213188201</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.0001334526910548289</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -646,29 +652,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.007470683708903277</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.937091197937183e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.003168171690874954</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0062820907408898</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.039905455642576e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.004500659347109801</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -678,28 +672,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.07584242857359601</v>
+        <v>0.007470683708903277</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005589860579383</v>
+        <v>7.937091197937183e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0288833029545226</v>
+        <v>0.003168171690874954</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0398321786500645</v>
+        <v>0.0062820907408898</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003050655832605</v>
+        <v>5.039905455642576e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0437396477109587</v>
+        <v>0.004500659347109801</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -707,20 +701,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.001572628624304701</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.07584242857359601</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005589860579383</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0288833029545226</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0398321786500645</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0003050655832605</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0437396477109587</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -729,7 +733,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.001047081741485413</v>
+        <v>0.001572628624304701</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -741,7 +745,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -750,83 +754,91 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.003004192937968216</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.08548486513694213</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0006383569699176719</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.03205147595173372</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.04645631082290141</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0003554646378169257</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.0482403070580685</v>
-      </c>
+        <v>0.01288407882297164</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.002053604010160708</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.001047081741485413</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>1.093547660215742e-07</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0002577736165919</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0006444730100779027</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.005579396866169524</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01668574752361535</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.08548486513694213</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0006383569699176719</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.03205147595173372</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.04645631082290141</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0003554646378169257</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0482403070580685</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.000395441316293494</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.005735747136105064</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0007986712993011486</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -837,7 +849,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -847,12 +859,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>7.322806083117311e-10</v>
+        <v>0.002053604010160708</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1.093547660215742e-07</v>
+      </c>
       <c r="I17" t="n">
-        <v>8.152913431792302e-11</v>
+        <v>0.0002577736165919</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -860,7 +874,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -868,24 +882,18 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.001497759788412087</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0001417368229084807</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>5.615015649739315e-05</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -894,21 +902,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0008703050421561751</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0.0001420473188329681</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -917,17 +921,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>7.322806083117311e-10</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>8.152913431792302e-11</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -935,30 +943,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.001497759788412087</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.003109201685836332</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.000129387680729</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0038806073302648</v>
-      </c>
+        <v>0.0001417368229084807</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0041737399182243</v>
-      </c>
-      <c r="J21" t="n">
-        <v>6.122667160201211e-05</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.005115832688583799</v>
-      </c>
+        <v>5.615015649739315e-05</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -968,28 +970,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.020121667103184</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0006009410903166</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.027242133265133</v>
-      </c>
+        <v>0.0008703050421561751</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0179156096703749</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.000270718412435</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0423519848862636</v>
-      </c>
+        <v>0.0001420473188329681</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -997,9 +991,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.001564790190102735</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1010,7 +1002,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1018,20 +1010,30 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.00407055340951407</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.003109201685836332</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.000129387680729</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0038806073302648</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0041737399182243</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6.122667160201211e-05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.005115832688583799</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1039,65 +1041,61 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>0.007133103388028891</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.02629651539652631</v>
+        <v>0.020121667103184</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0007303287710456</v>
+        <v>0.0006009410903166</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03112284995016382</v>
+        <v>0.027242133265133</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0225453207620506</v>
+        <v>0.0179156096703749</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0003319450840370121</v>
+        <v>0.000270718412435</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0474678175748474</v>
+        <v>0.0423519848862636</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0028429310518253</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.001564790190102735</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>1.853475200557468e-07</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0004117404118114</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.008352469796889231</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1108,15 +1106,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.00407055340951407</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1127,55 +1127,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.000395441316293494</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.005735747136105064</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.01628424448421927</v>
+      </c>
       <c r="F29" t="n">
-        <v>5.159994887463009e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.02629651539652631</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0007303287710456</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.03112284995016382</v>
+      </c>
       <c r="I29" t="n">
-        <v>2.181042364749701e-09</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.0225453207620506</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0003319450840370121</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0474678175748474</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>6.84762391541253e-05</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.005941026541683417</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.003608512460127723</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2.200879955645684e-05</v>
-      </c>
+        <v>0.0008002409739039778</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>1.599038756056599e-05</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1185,12 +1199,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>4.522630829141753e-05</v>
+        <v>0.0028429310518253</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>1.853475200557468e-07</v>
+      </c>
       <c r="I31" t="n">
-        <v>5.229533163129361e-05</v>
+        <v>0.0004117404118114</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1198,7 +1214,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1207,29 +1223,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>1.721647041242079e-11</v>
-      </c>
-      <c r="G32" t="n">
-        <v>4.764648946044249e-12</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.475616247131327e-10</v>
-      </c>
-      <c r="I32" t="n">
-        <v>6.85489413995898e-11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>4.193308022998501e-13</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.671568424888381e-10</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1238,29 +1242,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.000273505592033718</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.0002311930686831</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0051125507058801</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0010779854908764</v>
-      </c>
-      <c r="J33" t="n">
-        <v>7.874719523598319e-05</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0072768487878193</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1270,28 +1262,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0010985726600198</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0005420234133979</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0246011132586586</v>
-      </c>
+        <v>5.159994887463009e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0031809784935991</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0002330211164886</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0393920586321853</v>
-      </c>
+        <v>2.181042364749701e-09</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1300,19 +1284,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.001549435461082234</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.003608512460127723</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.200879955645684e-05</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>1.599038756056599e-05</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1320,20 +1308,22 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.009801744138411114</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>4.522630829141753e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>5.229533163129361e-05</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1341,25 +1331,183 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>0.01495969205962107</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>1.721647041242079e-11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.764648946044249e-12</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.475616247131327e-10</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.85489413995898e-11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.193308022998501e-13</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.671568424888381e-10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.000273505592033718</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0002311930686831</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0051125507058801</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0010779854908764</v>
+      </c>
+      <c r="J38" t="n">
+        <v>7.874719523598319e-05</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0072768487878193</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0010985726600198</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0005420234133979</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0246011132586586</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0031809784935991</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0002330211164886</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.0393920586321853</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.001549435461082234</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.009801744138411114</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>6.84762391541253e-05</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.005941026541683417</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.01575993303352505</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.00428224958893805</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.0007732164868456489</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.02971384945962038</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.004738992365070066</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.000311768312143914</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.04666890778716144</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_DK.xlsx
+++ b/Outputs/PtX_demand_DK.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.0007974757626754852</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.009463564721319536</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0032139590089694</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0027573584833741</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0004567236479811</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -724,7 +732,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -733,7 +741,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.001572628624304701</v>
+        <v>0.01288407882297164</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -745,7 +753,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -754,7 +762,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.01288407882297164</v>
+        <v>0.001572628624304701</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -803,19 +811,19 @@
         <v>0.01668574752361535</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08548486513694213</v>
+        <v>0.09494842985826167</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006383569699176719</v>
+        <v>0.003852315978887072</v>
       </c>
       <c r="H15" t="n">
         <v>0.03205147595173372</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04645631082290141</v>
+        <v>0.04921366930627552</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0003554646378169257</v>
+        <v>0.0008121882857980258</v>
       </c>
       <c r="K15" t="n">
         <v>0.0482403070580685</v>
@@ -839,11 +847,19 @@
       <c r="E16" t="n">
         <v>0.0007986712993011486</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.02681850974619529</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0037718773416514</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0096288164631719</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0004504356537378</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1064,7 +1080,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1073,7 +1089,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.001564790190102735</v>
+        <v>0.008352469796889231</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1085,7 +1101,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1094,7 +1110,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.008352469796889231</v>
+        <v>0.001564790190102735</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1143,19 +1159,19 @@
         <v>0.01628424448421927</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02629651539652631</v>
+        <v>0.0531150251427216</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0007303287710456</v>
+        <v>0.004502206112697</v>
       </c>
       <c r="H29" t="n">
         <v>0.03112284995016382</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0225453207620506</v>
+        <v>0.0321741372252225</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0003319450840370121</v>
+        <v>0.0007823807377748121</v>
       </c>
       <c r="K29" t="n">
         <v>0.0474678175748474</v>
@@ -1179,11 +1195,19 @@
       <c r="E30" t="n">
         <v>0.0008002409739039778</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.03114002015922527</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0042357962099098</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0144075145076808</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0004600407709618</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1416,7 +1440,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1424,9 +1448,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.001549435461082234</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1437,7 +1459,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1445,7 +1467,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.001549435461082234</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1493,19 +1517,19 @@
         <v>0.01575993303352505</v>
       </c>
       <c r="F43" t="n">
-        <v>0.00428224958893805</v>
+        <v>0.03542226974816332</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0007732164868456489</v>
+        <v>0.005009012696755449</v>
       </c>
       <c r="H43" t="n">
         <v>0.02971384945962038</v>
       </c>
       <c r="I43" t="n">
-        <v>0.004738992365070066</v>
+        <v>0.01914650687275087</v>
       </c>
       <c r="J43" t="n">
-        <v>0.000311768312143914</v>
+        <v>0.000771809083105714</v>
       </c>
       <c r="K43" t="n">
         <v>0.04666890778716144</v>
